--- a/output/pdf_financials_xlsx/IOT.xlsx
+++ b/output/pdf_financials_xlsx/IOT.xlsx
@@ -1035,40 +1035,40 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012113</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006114</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002306</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000304</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000108</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>4.3e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.017566</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.008954</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.012756</v>
@@ -2005,40 +2005,40 @@
         <v>-1.127203</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.164036</v>
+        <v>-1.176149</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.176899</v>
+        <v>-1.183013</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.497723</v>
+        <v>-1.500029</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.827255</v>
+        <v>-0.827559</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.20964</v>
+        <v>-0.209684</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.250605</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.215535</v>
+        <v>-0.215643</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.753385</v>
+        <v>0.753342</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.127634</v>
+        <v>-0.127637</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.048761</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.36713</v>
+        <v>0.349564</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.136511</v>
+        <v>-0.145465</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.170338</v>
@@ -2121,40 +2121,40 @@
         <v>-1.127203</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.164036</v>
+        <v>-1.176149</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.117044</v>
+        <v>-1.123158</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.435941</v>
+        <v>-1.438247</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.772097</v>
+        <v>-0.772401</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.159811</v>
+        <v>-0.159855</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.207886</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.196095</v>
+        <v>-0.196203</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.770212</v>
+        <v>0.770169</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.112266</v>
+        <v>-0.112269</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.035476</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.438025</v>
+        <v>0.420459</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.022346</v>
+        <v>-0.0313</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.092074</v>
@@ -2179,40 +2179,40 @@
         <v>-77.52833022909039</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-72.97793426170432</v>
+        <v>-73.73734524015518</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-102.678450783846</v>
+        <v>-103.2404483847395</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-165.3186198321418</v>
+        <v>-165.5841075766472</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-86.86793794448126</v>
+        <v>-86.90214071062996</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-28.13276766538746</v>
+        <v>-28.1405133260571</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-47.56420112386287</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-19.50033711284231</v>
+        <v>-19.51107699100436</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>77.77224658527399</v>
+        <v>77.7679046552558</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-13.57615773912097</v>
+        <v>-13.57652052458779</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-3.597150751603336</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>29.56099035813323</v>
+        <v>28.37551382909729</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-1.984876706877607</v>
+        <v>-2.780213054921199</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-7.785515697190673</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.120859</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.375559</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.375559</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.120859</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.375559</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.375559</v>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.20769</v>
+        <v>0.08683100000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.530135</v>
+        <v>0.154576</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.144175</v>
@@ -18907,7 +18907,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -44569,7 +44569,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -44668,7 +44668,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -45664,7 +45664,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -45767,7 +45767,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -47046,7 +47046,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -47147,7 +47147,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -47535,7 +47535,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -47842,7 +47842,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">

--- a/output/pdf_financials_xlsx/IOT.xlsx
+++ b/output/pdf_financials_xlsx/IOT.xlsx
@@ -2744,13 +2744,13 @@
         <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.003508</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.101941</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.180664</v>
       </c>
     </row>
     <row r="41">
@@ -2802,13 +2802,13 @@
         <v>0.197758</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.207844</v>
+        <v>0.211352</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0.638014</v>
+        <v>0.739955</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0.6883</v>
+        <v>0.868964</v>
       </c>
     </row>
     <row r="42">
@@ -3208,13 +3208,13 @@
         <v>0.03538</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.058608</v>
+        <v>0.0551</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.185177</v>
+        <v>0.083236</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.529091</v>
+        <v>0.348427</v>
       </c>
     </row>
     <row r="49">
@@ -7017,22 +7017,22 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07688</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01726</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.051445</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.063051</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024806</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007442</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -7044,13 +7044,13 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013662</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009317000000000001</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002438</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>-0.06014</v>
@@ -7355,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="117">
@@ -8391,22 +8391,22 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07688</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01726</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.051445</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.063051</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024806</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007442</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8418,13 +8418,13 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013662</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009317000000000001</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002438</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>-0.06014</v>
@@ -8454,19 +8454,19 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.136849</v>
+        <v>-1.154109</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.9378570000000001</v>
+        <v>-0.989302</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.41576</v>
+        <v>-1.478811</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.07916</v>
+        <v>-1.103966</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.560955</v>
+        <v>-0.568397</v>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
@@ -8482,13 +8482,13 @@
         <v>0.002317</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.158685</v>
+        <v>-0.172347</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.280747</v>
+        <v>-0.290064</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.073862</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-0.035096</v>
@@ -28994,7 +28994,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -30843,7 +30847,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -33912,7 +33920,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="n">
         <v>-0.07688</v>
       </c>
@@ -34888,7 +34900,11 @@
           <t>Purchase of equipment (note 7)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
